--- a/Monthly_Budgeting_Forecasting/Monthly_Budget_Forecasting_Tool.xlsx
+++ b/Monthly_Budgeting_Forecasting/Monthly_Budget_Forecasting_Tool.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Magic\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Magic\OneDrive\Documents\GitHub\Financial-Analysis-Portfolio\Monthly_Budgeting_Forecasting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC5354B-A739-41D8-A643-E380C7CE3556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A16AAD6-907A-4213-BC67-F1B6A168656D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Live Denamic" sheetId="4" r:id="rId3"/>
     <sheet name="Income Statement" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -560,12 +560,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -574,6 +568,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
@@ -876,7 +876,7 @@
       <c r="B2" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="47">
+      <c r="C2" s="45">
         <v>46291</v>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       <c r="B13" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="46">
         <v>0.3</v>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       <c r="B26" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="48">
+      <c r="C26" s="46">
         <v>0.2</v>
       </c>
     </row>
@@ -3394,13 +3394,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="44"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
@@ -3541,51 +3541,51 @@
       </c>
       <c r="I6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!I4,Forecast!I17,Forecast!I30)</f>
-        <v>26859.76114072718</v>
+        <v>18801.832798509025</v>
       </c>
       <c r="J6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!J4,Forecast!J17,Forecast!J30)</f>
-        <v>26922.593568760843</v>
+        <v>18845.81549813259</v>
       </c>
       <c r="K6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!K4,Forecast!K17,Forecast!K30)</f>
-        <v>28560.219908935931</v>
+        <v>19992.153936255152</v>
       </c>
       <c r="L6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!L4,Forecast!L17,Forecast!L30)</f>
-        <v>28501.43193285961</v>
+        <v>19951.002353001724</v>
       </c>
       <c r="M6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!M4,Forecast!M17,Forecast!M30)</f>
-        <v>30101.347009231198</v>
+        <v>21070.942906461838</v>
       </c>
       <c r="N6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!N4,Forecast!N17,Forecast!N30)</f>
-        <v>30111.719199725641</v>
+        <v>21078.203439807949</v>
       </c>
       <c r="O6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!O4,Forecast!O17,Forecast!O30)</f>
-        <v>31672.189468797595</v>
+        <v>22170.532628158315</v>
       </c>
       <c r="P6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!P4,Forecast!P17,Forecast!P30)</f>
-        <v>31683.438885965574</v>
+        <v>22178.407220175901</v>
       </c>
       <c r="Q6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!Q4,Forecast!Q17,Forecast!Q30)</f>
-        <v>33240.958001217623</v>
+        <v>23268.670600852336</v>
       </c>
       <c r="R6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!R4,Forecast!R17,Forecast!R30)</f>
-        <v>33250.813004448624</v>
+        <v>23275.569103114034</v>
       </c>
       <c r="S6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!S4,Forecast!S17,Forecast!S30)</f>
-        <v>34807.508552965461</v>
+        <v>24365.25598707582</v>
       </c>
       <c r="T6" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!T4,Forecast!T17,Forecast!T30)</f>
-        <v>34816.870479844321</v>
+        <v>24371.809335891023</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -3619,51 +3619,51 @@
       </c>
       <c r="I7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!I5,Forecast!I18,Forecast!I31)</f>
-        <v>48858.543636264534</v>
+        <v>34200.980545385173</v>
       </c>
       <c r="J7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!J5,Forecast!J18,Forecast!J31)</f>
-        <v>47585.966401114296</v>
+        <v>33310.176480780006</v>
       </c>
       <c r="K7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!K5,Forecast!K18,Forecast!K31)</f>
-        <v>45844.020740193344</v>
+        <v>32090.814518135339</v>
       </c>
       <c r="L7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!L5,Forecast!L18,Forecast!L31)</f>
-        <v>44591.390961671706</v>
+        <v>31213.973673170192</v>
       </c>
       <c r="M7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!M5,Forecast!M18,Forecast!M31)</f>
-        <v>42871.654516645998</v>
+        <v>30010.158161652198</v>
       </c>
       <c r="N7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!N5,Forecast!N18,Forecast!N31)</f>
-        <v>41659.494546522692</v>
+        <v>29161.646182565881</v>
       </c>
       <c r="O7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!O5,Forecast!O18,Forecast!O31)</f>
-        <v>39701.198358000329</v>
+        <v>27790.83885060023</v>
       </c>
       <c r="P7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!P5,Forecast!P18,Forecast!P31)</f>
-        <v>38527.277316495951</v>
+        <v>26969.094121547165</v>
       </c>
       <c r="Q7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!Q5,Forecast!Q18,Forecast!Q31)</f>
-        <v>36611.983520530979</v>
+        <v>25628.388464371685</v>
       </c>
       <c r="R7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!R5,Forecast!R18,Forecast!R31)</f>
-        <v>35383.991475539748</v>
+        <v>24768.79403287782</v>
       </c>
       <c r="S7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!S5,Forecast!S18,Forecast!S31)</f>
-        <v>33666.209348543103</v>
+        <v>23566.346543980169</v>
       </c>
       <c r="T7" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!T5,Forecast!T18,Forecast!T31)</f>
-        <v>32319.265697321396</v>
+        <v>22623.485988124976</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -3697,51 +3697,51 @@
       </c>
       <c r="I8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!I6,Forecast!I19,Forecast!I32)</f>
-        <v>41183.971201358247</v>
+        <v>28828.77984095077</v>
       </c>
       <c r="J8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!J6,Forecast!J19,Forecast!J32)</f>
-        <v>42613.671663537316</v>
+        <v>29829.570164476117</v>
       </c>
       <c r="K8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!K6,Forecast!K19,Forecast!K32)</f>
-        <v>44036.167863863549</v>
+        <v>30825.317504704482</v>
       </c>
       <c r="L8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!L6,Forecast!L19,Forecast!L32)</f>
-        <v>45413.911842965106</v>
+        <v>31789.738290075573</v>
       </c>
       <c r="M8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!M6,Forecast!M19,Forecast!M32)</f>
-        <v>46814.567474384923</v>
+        <v>32770.197232069448</v>
       </c>
       <c r="N8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!N6,Forecast!N19,Forecast!N32)</f>
-        <v>48215.310791421689</v>
+        <v>33750.717553995179</v>
       </c>
       <c r="O8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!O6,Forecast!O19,Forecast!O32)</f>
-        <v>49616.147650724932</v>
+        <v>34731.303355507451</v>
       </c>
       <c r="P8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!P6,Forecast!P19,Forecast!P32)</f>
-        <v>51017.051728752886</v>
+        <v>35711.936210127016</v>
       </c>
       <c r="Q8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!Q6,Forecast!Q19,Forecast!Q32)</f>
-        <v>52417.99544853883</v>
+        <v>36692.596813977179</v>
       </c>
       <c r="R8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!R6,Forecast!R19,Forecast!R32)</f>
-        <v>53818.957103207329</v>
+        <v>37673.269972245129</v>
       </c>
       <c r="S8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!S6,Forecast!S19,Forecast!S32)</f>
-        <v>55219.921179946665</v>
+        <v>38653.944825962666</v>
       </c>
       <c r="T8" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!T6,Forecast!T19,Forecast!T32)</f>
-        <v>56620.877094019284</v>
+        <v>39634.6139658135</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -3775,51 +3775,51 @@
       </c>
       <c r="I9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!I7,Forecast!I20,Forecast!I33)</f>
-        <v>78427.891551870402</v>
+        <v>54899.524086309277</v>
       </c>
       <c r="J9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!J7,Forecast!J20,Forecast!J33)</f>
-        <v>76178.043433908766</v>
+        <v>53324.630403736133</v>
       </c>
       <c r="K9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!K7,Forecast!K20,Forecast!K33)</f>
-        <v>73912.46503670323</v>
+        <v>51738.725525692258</v>
       </c>
       <c r="L9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!L7,Forecast!L20,Forecast!L33)</f>
-        <v>71611.910305970319</v>
+        <v>50128.337214179221</v>
       </c>
       <c r="M9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!M7,Forecast!M20,Forecast!M33)</f>
-        <v>69331.893003484322</v>
+        <v>48532.325102439019</v>
       </c>
       <c r="N9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!N7,Forecast!N20,Forecast!N33)</f>
-        <v>67050.574891618191</v>
+        <v>46935.402424132728</v>
       </c>
       <c r="O9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!O7,Forecast!O20,Forecast!O33)</f>
-        <v>64768.400572645376</v>
+        <v>45337.880400851762</v>
       </c>
       <c r="P9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!P7,Forecast!P20,Forecast!P33)</f>
-        <v>62480.728984662957</v>
+        <v>43736.510289264064</v>
       </c>
       <c r="Q9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!Q7,Forecast!Q20,Forecast!Q33)</f>
-        <v>60196.664077393398</v>
+        <v>42137.664854175375</v>
       </c>
       <c r="R9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!R7,Forecast!R20,Forecast!R33)</f>
-        <v>57912.678103935665</v>
+        <v>40538.874672754966</v>
       </c>
       <c r="S9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!S7,Forecast!S20,Forecast!S33)</f>
-        <v>55628.736825287509</v>
+        <v>38940.115777701256</v>
       </c>
       <c r="T9" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!T7,Forecast!T20,Forecast!T33)</f>
-        <v>53344.816264503774</v>
+        <v>37341.371385152641</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -3853,51 +3853,51 @@
       </c>
       <c r="I10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!I8,Forecast!I21,Forecast!I34)</f>
-        <v>81916.876517986253</v>
+        <v>57341.813562590374</v>
       </c>
       <c r="J10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!J8,Forecast!J21,Forecast!J34)</f>
-        <v>79206.407798523505</v>
+        <v>55444.485458966454</v>
       </c>
       <c r="K10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!K8,Forecast!K21,Forecast!K34)</f>
-        <v>76483.449900994485</v>
+        <v>53538.414930696134</v>
       </c>
       <c r="L10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!L8,Forecast!L21,Forecast!L34)</f>
-        <v>73792.487928073344</v>
+        <v>51654.741549651335</v>
       </c>
       <c r="M10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!M8,Forecast!M21,Forecast!M34)</f>
-        <v>71086.197541592934</v>
+        <v>49760.338279115051</v>
       </c>
       <c r="N10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!N8,Forecast!N21,Forecast!N34)</f>
-        <v>68267.760676605714</v>
+        <v>47787.432473623994</v>
       </c>
       <c r="O10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!O8,Forecast!O21,Forecast!O34)</f>
-        <v>65623.680287821815</v>
+        <v>45936.576201475269</v>
       </c>
       <c r="P10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!P8,Forecast!P21,Forecast!P34)</f>
-        <v>62955.10938603519</v>
+        <v>44068.576570224628</v>
       </c>
       <c r="Q10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!Q8,Forecast!Q21,Forecast!Q34)</f>
-        <v>60216.206521543558</v>
+        <v>42151.344565080486</v>
       </c>
       <c r="R10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!R8,Forecast!R21,Forecast!R34)</f>
-        <v>57505.992999262417</v>
+        <v>40254.195099483688</v>
       </c>
       <c r="S10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!S8,Forecast!S21,Forecast!S34)</f>
-        <v>54795.850819817926</v>
+        <v>38357.095573872546</v>
       </c>
       <c r="T10" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!T8,Forecast!T21,Forecast!T34)</f>
-        <v>51987.349634165374</v>
+        <v>36391.144743915756</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -3931,51 +3931,51 @@
       </c>
       <c r="I11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!I9,Forecast!I22,Forecast!I35)</f>
-        <v>20784.676716073132</v>
+        <v>14549.273701251192</v>
       </c>
       <c r="J11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!J9,Forecast!J22,Forecast!J35)</f>
-        <v>18966.367329335342</v>
+        <v>13276.457130534738</v>
       </c>
       <c r="K11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!K9,Forecast!K22,Forecast!K35)</f>
-        <v>17138.76514187401</v>
+        <v>11997.135599311807</v>
       </c>
       <c r="L11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!L9,Forecast!L22,Forecast!L35)</f>
-        <v>15398.473034721901</v>
+        <v>10778.931124305331</v>
       </c>
       <c r="M11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!M9,Forecast!M22,Forecast!M35)</f>
-        <v>13625.108196978312</v>
+        <v>9537.5757378848175</v>
       </c>
       <c r="N11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!N9,Forecast!N22,Forecast!N35)</f>
-        <v>11459.690736972156</v>
+        <v>8021.7835158805083</v>
       </c>
       <c r="O11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!O9,Forecast!O22,Forecast!O35)</f>
-        <v>10235.713818413371</v>
+        <v>7164.9996728893593</v>
       </c>
       <c r="P11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!P9,Forecast!P22,Forecast!P35)</f>
-        <v>8271.2763181428709</v>
+        <v>5789.8934227000091</v>
       </c>
       <c r="Q11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!Q9,Forecast!Q22,Forecast!Q35)</f>
-        <v>6108.360191654755</v>
+        <v>4275.8521341583282</v>
       </c>
       <c r="R11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!R9,Forecast!R22,Forecast!R35)</f>
-        <v>4830.7593279369239</v>
+        <v>3381.5315295558466</v>
       </c>
       <c r="S11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!S9,Forecast!S22,Forecast!S35)</f>
-        <v>2887.1373473223803</v>
+        <v>2020.9961431256661</v>
       </c>
       <c r="T11" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!T9,Forecast!T22,Forecast!T35)</f>
-        <v>825.90661841332144</v>
+        <v>578.13463288932496</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -4009,51 +4009,51 @@
       </c>
       <c r="I12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!I10,Forecast!I23,Forecast!I36)</f>
-        <v>46256.946961125286</v>
+        <v>32379.862872787697</v>
       </c>
       <c r="J12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!J10,Forecast!J23,Forecast!J36)</f>
-        <v>47704.637988354101</v>
+        <v>33393.24659184787</v>
       </c>
       <c r="K12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!K10,Forecast!K23,Forecast!K36)</f>
-        <v>49150.17146376762</v>
+        <v>34405.120024637334</v>
       </c>
       <c r="L12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!L10,Forecast!L23,Forecast!L36)</f>
-        <v>50452.328668162765</v>
+        <v>35316.63006771393</v>
       </c>
       <c r="M12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!M10,Forecast!M23,Forecast!M36)</f>
-        <v>51824.34271783955</v>
+        <v>36277.039902487682</v>
       </c>
       <c r="N12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!N10,Forecast!N23,Forecast!N36)</f>
-        <v>53196.599428618836</v>
+        <v>37237.619600033184</v>
       </c>
       <c r="O12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!O10,Forecast!O23,Forecast!O36)</f>
-        <v>54569.117070491142</v>
+        <v>38198.381949343799</v>
       </c>
       <c r="P12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!P10,Forecast!P23,Forecast!P36)</f>
-        <v>55941.820354912226</v>
+        <v>39159.274248438553</v>
       </c>
       <c r="Q12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!Q10,Forecast!Q23,Forecast!Q36)</f>
-        <v>57314.630177163723</v>
+        <v>40120.241124014603</v>
       </c>
       <c r="R12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!R10,Forecast!R23,Forecast!R36)</f>
-        <v>58687.484315531168</v>
+        <v>41081.239020871813</v>
       </c>
       <c r="S12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!S10,Forecast!S23,Forecast!S36)</f>
-        <v>60060.338401168861</v>
+        <v>42042.2368808182</v>
       </c>
       <c r="T12" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!T10,Forecast!T23,Forecast!T36)</f>
-        <v>61433.162269303619</v>
+        <v>43003.213588512532</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -4087,51 +4087,51 @@
       </c>
       <c r="I13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!I11,Forecast!I24,Forecast!I37)</f>
-        <v>76705.606550771539</v>
+        <v>53693.924585540073</v>
       </c>
       <c r="J13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!J11,Forecast!J24,Forecast!J37)</f>
-        <v>80731.326035333477</v>
+        <v>56511.928224733434</v>
       </c>
       <c r="K13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!K11,Forecast!K24,Forecast!K37)</f>
-        <v>87089.65779041838</v>
+        <v>60962.76045329286</v>
       </c>
       <c r="L13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!L11,Forecast!L24,Forecast!L37)</f>
-        <v>90875.730395796971</v>
+        <v>63613.011277057878</v>
       </c>
       <c r="M13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!M11,Forecast!M24,Forecast!M37)</f>
-        <v>96948.062430063554</v>
+        <v>67863.643701044479</v>
       </c>
       <c r="N13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!N11,Forecast!N24,Forecast!N37)</f>
-        <v>100800.21730959584</v>
+        <v>70560.152116717087</v>
       </c>
       <c r="O13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!O11,Forecast!O24,Forecast!O37)</f>
-        <v>106865.98156559149</v>
+        <v>74806.187095914036</v>
       </c>
       <c r="P13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!P11,Forecast!P24,Forecast!P37)</f>
-        <v>111036.0335243259</v>
+        <v>77725.223467028132</v>
       </c>
       <c r="Q13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!Q11,Forecast!Q24,Forecast!Q37)</f>
-        <v>117072.50922037291</v>
+        <v>81950.756454261034</v>
       </c>
       <c r="R13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!R11,Forecast!R24,Forecast!R37)</f>
-        <v>120138.49910544444</v>
+        <v>84096.949373811105</v>
       </c>
       <c r="S13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!S11,Forecast!S24,Forecast!S37)</f>
-        <v>126916.63408933014</v>
+        <v>88841.643862531098</v>
       </c>
       <c r="T13" s="21">
         <f>CHOOSE('Income Statement'!$C$2,Forecast!T11,Forecast!T24,Forecast!T37)</f>
-        <v>131085.87909406843</v>
+        <v>91760.115365847887</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -4200,11 +4200,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="46">
-        <v>1</v>
+      <c r="C2" s="44">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -4286,51 +4286,51 @@
       </c>
       <c r="C6" s="16">
         <f t="shared" ref="C6:N6" si="0">C31</f>
-        <v>630985.87314159761</v>
+        <v>441690.11119911837</v>
       </c>
       <c r="D6" s="16">
         <f t="shared" si="0"/>
-        <v>620904.6664156263</v>
+        <v>434633.26649093837</v>
       </c>
       <c r="E6" s="16">
         <f t="shared" si="0"/>
-        <v>620035.33874274394</v>
+        <v>434024.73711992078</v>
       </c>
       <c r="F6" s="16">
         <f t="shared" si="0"/>
-        <v>609106.85745442763</v>
+        <v>426374.80021809932</v>
       </c>
       <c r="G6" s="16">
         <f t="shared" si="0"/>
-        <v>608108.34604897664</v>
+        <v>425675.84223428363</v>
       </c>
       <c r="H6" s="16">
         <f t="shared" si="0"/>
-        <v>598093.44788540283</v>
+        <v>418665.41351978196</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="0"/>
-        <v>799381.94366013689</v>
+        <v>559567.36056209577</v>
       </c>
       <c r="J6" s="16">
         <f t="shared" si="0"/>
-        <v>786360.02146756905</v>
+        <v>550452.01502729836</v>
       </c>
       <c r="K6" s="16">
         <f t="shared" si="0"/>
-        <v>782352.94504358445</v>
+        <v>547647.06153050903</v>
       </c>
       <c r="L6" s="16">
         <f t="shared" si="0"/>
-        <v>768709.81017586985</v>
+        <v>538096.86712310871</v>
       </c>
       <c r="M6" s="16">
         <f t="shared" si="0"/>
-        <v>766905.64049689576</v>
+        <v>536833.94834782719</v>
       </c>
       <c r="N6" s="16">
         <f t="shared" si="0"/>
-        <v>751924.72518425609</v>
+        <v>526347.30762897921</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -4339,51 +4339,51 @@
       </c>
       <c r="C7" s="16">
         <f t="shared" ref="C7:N7" si="1">C35</f>
-        <v>126197.17462831952</v>
+        <v>88338.02223982368</v>
       </c>
       <c r="D7" s="16">
         <f t="shared" si="1"/>
-        <v>124180.93328312527</v>
+        <v>86926.653298187681</v>
       </c>
       <c r="E7" s="16">
         <f t="shared" si="1"/>
-        <v>124007.0677485488</v>
+        <v>86804.947423984166</v>
       </c>
       <c r="F7" s="16">
         <f t="shared" si="1"/>
-        <v>121821.37149088553</v>
+        <v>85274.960043619867</v>
       </c>
       <c r="G7" s="16">
         <f t="shared" si="1"/>
-        <v>121621.66920979533</v>
+        <v>85135.168446856725</v>
       </c>
       <c r="H7" s="16">
         <f t="shared" si="1"/>
-        <v>119618.68957708057</v>
+        <v>83733.082703956403</v>
       </c>
       <c r="I7" s="16">
         <f t="shared" si="1"/>
-        <v>159876.38873202738</v>
+        <v>111913.47211241916</v>
       </c>
       <c r="J7" s="16">
         <f t="shared" si="1"/>
-        <v>157272.00429351383</v>
+        <v>110090.40300545968</v>
       </c>
       <c r="K7" s="16">
         <f t="shared" si="1"/>
-        <v>156470.5890087169</v>
+        <v>109529.41230610182</v>
       </c>
       <c r="L7" s="16">
         <f t="shared" si="1"/>
-        <v>153741.96203517399</v>
+        <v>107619.37342462175</v>
       </c>
       <c r="M7" s="16">
         <f t="shared" si="1"/>
-        <v>153381.12809937916</v>
+        <v>107366.78966956545</v>
       </c>
       <c r="N7" s="16">
         <f t="shared" si="1"/>
-        <v>150384.94503685122</v>
+        <v>105269.46152579585</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -4392,51 +4392,51 @@
       </c>
       <c r="C8" s="39">
         <f t="shared" ref="C8:N8" si="2">C6-C7</f>
-        <v>504788.6985132781</v>
+        <v>353352.08895929472</v>
       </c>
       <c r="D8" s="39">
         <f t="shared" si="2"/>
-        <v>496723.73313250102</v>
+        <v>347706.61319275072</v>
       </c>
       <c r="E8" s="39">
         <f t="shared" si="2"/>
-        <v>496028.27099419513</v>
+        <v>347219.7896959366</v>
       </c>
       <c r="F8" s="39">
         <f t="shared" si="2"/>
-        <v>487285.48596354213</v>
+        <v>341099.84017447947</v>
       </c>
       <c r="G8" s="39">
         <f t="shared" si="2"/>
-        <v>486486.67683918134</v>
+        <v>340540.6737874269</v>
       </c>
       <c r="H8" s="39">
         <f t="shared" si="2"/>
-        <v>478474.75830832229</v>
+        <v>334932.33081582555</v>
       </c>
       <c r="I8" s="39">
         <f t="shared" si="2"/>
-        <v>639505.55492810952</v>
+        <v>447653.88844967663</v>
       </c>
       <c r="J8" s="39">
         <f t="shared" si="2"/>
-        <v>629088.01717405522</v>
+        <v>440361.61202183866</v>
       </c>
       <c r="K8" s="39">
         <f t="shared" si="2"/>
-        <v>625882.35603486758</v>
+        <v>438117.64922440721</v>
       </c>
       <c r="L8" s="39">
         <f t="shared" si="2"/>
-        <v>614967.84814069583</v>
+        <v>430477.49369848694</v>
       </c>
       <c r="M8" s="39">
         <f t="shared" si="2"/>
-        <v>613524.51239751664</v>
+        <v>429467.15867826174</v>
       </c>
       <c r="N8" s="39">
         <f t="shared" si="2"/>
-        <v>601539.78014740488</v>
+        <v>421077.84610318334</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -4466,51 +4466,51 @@
       </c>
       <c r="C11" s="4">
         <f>SUMIFS('Live Denamic'!I$6:I$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>75718.304776991718</v>
+        <v>53002.813343894202</v>
       </c>
       <c r="D11" s="4">
         <f>SUMIFS('Live Denamic'!J$6:J$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>74508.559969875147</v>
+        <v>52155.9919789126</v>
       </c>
       <c r="E11" s="4">
         <f>SUMIFS('Live Denamic'!K$6:K$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>74404.240649129279</v>
+        <v>52082.968454390488</v>
       </c>
       <c r="F11" s="4">
         <f>SUMIFS('Live Denamic'!L$6:L$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>73092.822894531317</v>
+        <v>51164.97602617192</v>
       </c>
       <c r="G11" s="4">
         <f>SUMIFS('Live Denamic'!M$6:M$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>72973.001525877189</v>
+        <v>51081.101068114032</v>
       </c>
       <c r="H11" s="4">
         <f>SUMIFS('Live Denamic'!N$6:N$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>71771.213746248337</v>
+        <v>50239.849622373833</v>
       </c>
       <c r="I11" s="4">
         <f>SUMIFS('Live Denamic'!O$6:O$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>71373.387826797931</v>
+        <v>49961.371478758549</v>
       </c>
       <c r="J11" s="4">
         <f>SUMIFS('Live Denamic'!P$6:P$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>70210.716202461525</v>
+        <v>49147.501341723066</v>
       </c>
       <c r="K11" s="4">
         <f>SUMIFS('Live Denamic'!Q$6:Q$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>69852.941521748609</v>
+        <v>48897.059065224021</v>
       </c>
       <c r="L11" s="4">
         <f>SUMIFS('Live Denamic'!R$6:R$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>68634.804479988379</v>
+        <v>48044.363135991851</v>
       </c>
       <c r="M11" s="4">
         <f>SUMIFS('Live Denamic'!S$6:S$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>68473.717901508557</v>
+        <v>47931.602531055993</v>
       </c>
       <c r="N11" s="4">
         <f>SUMIFS('Live Denamic'!T$6:T$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B11)</f>
-        <v>67136.136177165725</v>
+        <v>46995.295324015999</v>
       </c>
       <c r="O11" s="15"/>
     </row>
@@ -4520,51 +4520,51 @@
       </c>
       <c r="C12" s="4">
         <f>SUMIFS('Live Denamic'!I$6:I$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>119611.86275322865</v>
+        <v>83728.303927260044</v>
       </c>
       <c r="D12" s="4">
         <f>SUMIFS('Live Denamic'!J$6:J$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>118791.71509744608</v>
+        <v>83154.200568212254</v>
       </c>
       <c r="E12" s="4">
         <f>SUMIFS('Live Denamic'!K$6:K$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>117948.63290056678</v>
+        <v>82564.043030396744</v>
       </c>
       <c r="F12" s="4">
         <f>SUMIFS('Live Denamic'!L$6:L$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>117025.82214893543</v>
+        <v>81918.075504254797</v>
       </c>
       <c r="G12" s="4">
         <f>SUMIFS('Live Denamic'!M$6:M$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>116146.46047786924</v>
+        <v>81302.522334508467</v>
       </c>
       <c r="H12" s="4">
         <f>SUMIFS('Live Denamic'!N$6:N$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>115265.88568303987</v>
+        <v>80686.119978127914</v>
       </c>
       <c r="I12" s="4">
         <f>SUMIFS('Live Denamic'!O$6:O$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>114384.54822337031</v>
+        <v>80069.183756359213</v>
       </c>
       <c r="J12" s="4">
         <f>SUMIFS('Live Denamic'!P$6:P$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>113497.78071341585</v>
+        <v>79448.446499391081</v>
       </c>
       <c r="K12" s="4">
         <f>SUMIFS('Live Denamic'!Q$6:Q$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>112614.65952593222</v>
+        <v>78830.261668152554</v>
       </c>
       <c r="L12" s="4">
         <f>SUMIFS('Live Denamic'!R$6:R$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>111731.635207143</v>
+        <v>78212.144645000095</v>
       </c>
       <c r="M12" s="4">
         <f>SUMIFS('Live Denamic'!S$6:S$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>110848.65800523417</v>
+        <v>77594.060603663922</v>
       </c>
       <c r="N12" s="4">
         <f>SUMIFS('Live Denamic'!T$6:T$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B12)</f>
-        <v>109965.69335852306</v>
+        <v>76975.985350966133</v>
       </c>
       <c r="O12" s="15"/>
     </row>
@@ -4574,51 +4574,51 @@
       </c>
       <c r="C13" s="4">
         <f>SUMIFS('Live Denamic'!I$6:I$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>102701.55323405939</v>
+        <v>71891.08726384156</v>
       </c>
       <c r="D13" s="4">
         <f>SUMIFS('Live Denamic'!J$6:J$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>98172.775127858855</v>
+        <v>68720.942589501195</v>
       </c>
       <c r="E13" s="4">
         <f>SUMIFS('Live Denamic'!K$6:K$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>93622.215042868498</v>
+        <v>65535.550530007939</v>
       </c>
       <c r="F13" s="4">
         <f>SUMIFS('Live Denamic'!L$6:L$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>89190.960962795245</v>
+        <v>62433.672673956666</v>
       </c>
       <c r="G13" s="4">
         <f>SUMIFS('Live Denamic'!M$6:M$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>84711.305738571245</v>
+        <v>59297.914016999872</v>
       </c>
       <c r="H13" s="4">
         <f>SUMIFS('Live Denamic'!N$6:N$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>79727.451413577874</v>
+        <v>55809.215989504504</v>
       </c>
       <c r="I13" s="4">
         <f>SUMIFS('Live Denamic'!O$6:O$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>75859.394106235181</v>
+        <v>53101.575874364629</v>
       </c>
       <c r="J13" s="4">
         <f>SUMIFS('Live Denamic'!P$6:P$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>71226.385704178057</v>
+        <v>49858.469992924634</v>
       </c>
       <c r="K13" s="4">
         <f>SUMIFS('Live Denamic'!Q$6:Q$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>66324.566713198306</v>
+        <v>46427.196699238812</v>
       </c>
       <c r="L13" s="4">
         <f>SUMIFS('Live Denamic'!R$6:R$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>62336.752327199341</v>
+        <v>43635.726629039535</v>
       </c>
       <c r="M13" s="4">
         <f>SUMIFS('Live Denamic'!S$6:S$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>57682.988167140305</v>
+        <v>40378.091716998213</v>
       </c>
       <c r="N13" s="4">
         <f>SUMIFS('Live Denamic'!T$6:T$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B13)</f>
-        <v>52813.256252578693</v>
+        <v>36969.279376805083</v>
       </c>
       <c r="O13" s="15"/>
     </row>
@@ -4628,51 +4628,51 @@
       </c>
       <c r="C14" s="4">
         <f>SUMIFS('Live Denamic'!I$6:I$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>122962.55351189683</v>
+        <v>86073.787458327773</v>
       </c>
       <c r="D14" s="4">
         <f>SUMIFS('Live Denamic'!J$6:J$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>128435.96402368759</v>
+        <v>89905.174816581304</v>
       </c>
       <c r="E14" s="4">
         <f>SUMIFS('Live Denamic'!K$6:K$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>136239.82925418601</v>
+        <v>95367.880477930186</v>
       </c>
       <c r="F14" s="4">
         <f>SUMIFS('Live Denamic'!L$6:L$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>141328.05906395975</v>
+        <v>98929.641344771808</v>
       </c>
       <c r="G14" s="4">
         <f>SUMIFS('Live Denamic'!M$6:M$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>148772.4051479031</v>
+        <v>104140.68360353216</v>
       </c>
       <c r="H14" s="4">
         <f>SUMIFS('Live Denamic'!N$6:N$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>153996.81673821469</v>
+        <v>107797.77171675027</v>
       </c>
       <c r="I14" s="4">
         <f>SUMIFS('Live Denamic'!O$6:O$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>161435.09863608264</v>
+        <v>113004.56904525784</v>
       </c>
       <c r="J14" s="4">
         <f>SUMIFS('Live Denamic'!P$6:P$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>166977.85387923813</v>
+        <v>116884.49771546668</v>
       </c>
       <c r="K14" s="4">
         <f>SUMIFS('Live Denamic'!Q$6:Q$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>174387.13939753664</v>
+        <v>122070.99757827564</v>
       </c>
       <c r="L14" s="4">
         <f>SUMIFS('Live Denamic'!R$6:R$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>178825.98342097562</v>
+        <v>125178.18839468292</v>
       </c>
       <c r="M14" s="4">
         <f>SUMIFS('Live Denamic'!S$6:S$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>186976.972490499</v>
+        <v>130883.88074334929</v>
       </c>
       <c r="N14" s="4">
         <f>SUMIFS('Live Denamic'!T$6:T$13,'Live Denamic'!$C$6:$C$13,'Income Statement'!$B14)</f>
-        <v>192519.04136337206</v>
+        <v>134763.32895436042</v>
       </c>
       <c r="O14" s="15"/>
     </row>
@@ -4682,51 +4682,51 @@
       </c>
       <c r="C15" s="40">
         <f t="shared" ref="C15:N15" si="3">SUM(C11:C14)</f>
-        <v>420994.27427617653</v>
+        <v>294695.99199332355</v>
       </c>
       <c r="D15" s="40">
         <f t="shared" si="3"/>
-        <v>419909.0142188677</v>
+        <v>293936.30995320738</v>
       </c>
       <c r="E15" s="40">
         <f t="shared" si="3"/>
-        <v>422214.91784675058</v>
+        <v>295550.44249272533</v>
       </c>
       <c r="F15" s="40">
         <f t="shared" si="3"/>
-        <v>420637.66507022176</v>
+        <v>294446.36554915516</v>
       </c>
       <c r="G15" s="40">
         <f t="shared" si="3"/>
-        <v>422603.17289022077</v>
+        <v>295822.2210231545</v>
       </c>
       <c r="H15" s="40">
         <f t="shared" si="3"/>
-        <v>420761.36758108076</v>
+        <v>294532.95730675652</v>
       </c>
       <c r="I15" s="40">
         <f t="shared" si="3"/>
-        <v>423052.42879248608</v>
+        <v>296136.70015474025</v>
       </c>
       <c r="J15" s="40">
         <f t="shared" si="3"/>
-        <v>421912.73649929359</v>
+        <v>295338.9155495055</v>
       </c>
       <c r="K15" s="40">
         <f t="shared" si="3"/>
-        <v>423179.30715841579</v>
+        <v>296225.51501089102</v>
       </c>
       <c r="L15" s="40">
         <f t="shared" si="3"/>
-        <v>421529.17543530633</v>
+        <v>295070.42280471441</v>
       </c>
       <c r="M15" s="40">
         <f t="shared" si="3"/>
-        <v>423982.33656438207</v>
+        <v>296787.6355950674</v>
       </c>
       <c r="N15" s="40">
         <f t="shared" si="3"/>
-        <v>422434.12715163955</v>
+        <v>295703.88900614763</v>
       </c>
       <c r="O15" s="15"/>
     </row>
@@ -4736,51 +4736,51 @@
       </c>
       <c r="C16" s="41">
         <f t="shared" ref="C16:N16" si="4">C8-C15</f>
-        <v>83794.424237101572</v>
+        <v>58656.09696597117</v>
       </c>
       <c r="D16" s="41">
         <f t="shared" si="4"/>
-        <v>76814.718913633318</v>
+        <v>53770.30323954334</v>
       </c>
       <c r="E16" s="41">
         <f t="shared" si="4"/>
-        <v>73813.353147444548</v>
+        <v>51669.347203211277</v>
       </c>
       <c r="F16" s="41">
         <f t="shared" si="4"/>
-        <v>66647.820893320371</v>
+        <v>46653.474625324307</v>
       </c>
       <c r="G16" s="41">
         <f t="shared" si="4"/>
-        <v>63883.50394896057</v>
+        <v>44718.452764272399</v>
       </c>
       <c r="H16" s="41">
         <f t="shared" si="4"/>
-        <v>57713.390727241524</v>
+        <v>40399.373509069032</v>
       </c>
       <c r="I16" s="41">
         <f t="shared" si="4"/>
-        <v>216453.12613562343</v>
+        <v>151517.18829493638</v>
       </c>
       <c r="J16" s="41">
         <f t="shared" si="4"/>
-        <v>207175.28067476163</v>
+        <v>145022.69647233316</v>
       </c>
       <c r="K16" s="41">
         <f t="shared" si="4"/>
-        <v>202703.04887645179</v>
+        <v>141892.1342135162</v>
       </c>
       <c r="L16" s="41">
         <f t="shared" si="4"/>
-        <v>193438.6727053895</v>
+        <v>135407.07089377253</v>
       </c>
       <c r="M16" s="41">
         <f t="shared" si="4"/>
-        <v>189542.17583313456</v>
+        <v>132679.52308319433</v>
       </c>
       <c r="N16" s="41">
         <f t="shared" si="4"/>
-        <v>179105.65299576533</v>
+        <v>125373.95709703572</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -4804,51 +4804,51 @@
       </c>
       <c r="C18" s="42">
         <f t="shared" ref="C18:N18" si="5">C38</f>
-        <v>3154.9293657079884</v>
+        <v>2208.4505559955919</v>
       </c>
       <c r="D18" s="42">
         <f t="shared" si="5"/>
-        <v>3104.5233320781317</v>
+        <v>2173.1663324546921</v>
       </c>
       <c r="E18" s="42">
         <f t="shared" si="5"/>
-        <v>3100.1766937137199</v>
+        <v>2170.1236855996044</v>
       </c>
       <c r="F18" s="42">
         <f t="shared" si="5"/>
-        <v>3045.5342872721385</v>
+        <v>2131.8740010904967</v>
       </c>
       <c r="G18" s="42">
         <f t="shared" si="5"/>
-        <v>3040.5417302448836</v>
+        <v>2128.3792111714183</v>
       </c>
       <c r="H18" s="42">
         <f t="shared" si="5"/>
-        <v>2990.4672394270146</v>
+        <v>2093.3270675989102</v>
       </c>
       <c r="I18" s="42">
         <f t="shared" si="5"/>
-        <v>3996.9097183006847</v>
+        <v>2797.8368028104792</v>
       </c>
       <c r="J18" s="42">
         <f t="shared" si="5"/>
-        <v>3931.8001073378459</v>
+        <v>2752.2600751364921</v>
       </c>
       <c r="K18" s="42">
         <f t="shared" si="5"/>
-        <v>3911.7647252179227</v>
+        <v>2738.2353076525455</v>
       </c>
       <c r="L18" s="42">
         <f t="shared" si="5"/>
-        <v>3843.54905087935</v>
+        <v>2690.4843356155438</v>
       </c>
       <c r="M18" s="42">
         <f t="shared" si="5"/>
-        <v>3834.5282024844792</v>
+        <v>2684.1697417391365</v>
       </c>
       <c r="N18" s="42">
         <f t="shared" si="5"/>
-        <v>3759.6236259212806</v>
+        <v>2631.7365381448963</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -4857,51 +4857,51 @@
       </c>
       <c r="C19" s="39">
         <f t="shared" ref="C19:N19" si="6">C16-C18</f>
-        <v>80639.494871393588</v>
+        <v>56447.646409975576</v>
       </c>
       <c r="D19" s="39">
         <f t="shared" si="6"/>
-        <v>73710.195581555192</v>
+        <v>51597.13690708865</v>
       </c>
       <c r="E19" s="39">
         <f t="shared" si="6"/>
-        <v>70713.176453730834</v>
+        <v>49499.223517611674</v>
       </c>
       <c r="F19" s="39">
         <f t="shared" si="6"/>
-        <v>63602.286606048234</v>
+        <v>44521.600624233812</v>
       </c>
       <c r="G19" s="39">
         <f t="shared" si="6"/>
-        <v>60842.962218715686</v>
+        <v>42590.073553100978</v>
       </c>
       <c r="H19" s="39">
         <f t="shared" si="6"/>
-        <v>54722.923487814507</v>
+        <v>38306.04644147012</v>
       </c>
       <c r="I19" s="39">
         <f t="shared" si="6"/>
-        <v>212456.21641732275</v>
+        <v>148719.35149212589</v>
       </c>
       <c r="J19" s="39">
         <f t="shared" si="6"/>
-        <v>203243.48056742377</v>
+        <v>142270.43639719667</v>
       </c>
       <c r="K19" s="39">
         <f t="shared" si="6"/>
-        <v>198791.28415123388</v>
+        <v>139153.89890586367</v>
       </c>
       <c r="L19" s="39">
         <f t="shared" si="6"/>
-        <v>189595.12365451016</v>
+        <v>132716.586558157</v>
       </c>
       <c r="M19" s="39">
         <f t="shared" si="6"/>
-        <v>185707.64763065008</v>
+        <v>129995.35334145519</v>
       </c>
       <c r="N19" s="39">
         <f t="shared" si="6"/>
-        <v>175346.02936984404</v>
+        <v>122742.22055889083</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -4925,51 +4925,51 @@
       </c>
       <c r="C21" s="42">
         <f t="shared" ref="C21:N21" si="7">C19*$C$40</f>
-        <v>20159.873717848397</v>
+        <v>14111.911602493894</v>
       </c>
       <c r="D21" s="42">
         <f t="shared" si="7"/>
-        <v>18427.548895388798</v>
+        <v>12899.284226772163</v>
       </c>
       <c r="E21" s="42">
         <f t="shared" si="7"/>
-        <v>17678.294113432708</v>
+        <v>12374.805879402918</v>
       </c>
       <c r="F21" s="42">
         <f t="shared" si="7"/>
-        <v>15900.571651512058</v>
+        <v>11130.400156058453</v>
       </c>
       <c r="G21" s="42">
         <f t="shared" si="7"/>
-        <v>15210.740554678921</v>
+        <v>10647.518388275244</v>
       </c>
       <c r="H21" s="42">
         <f t="shared" si="7"/>
-        <v>13680.730871953627</v>
+        <v>9576.51161036753</v>
       </c>
       <c r="I21" s="42">
         <f t="shared" si="7"/>
-        <v>53114.054104330688</v>
+        <v>37179.837873031473</v>
       </c>
       <c r="J21" s="42">
         <f t="shared" si="7"/>
-        <v>50810.870141855943</v>
+        <v>35567.609099299167</v>
       </c>
       <c r="K21" s="42">
         <f t="shared" si="7"/>
-        <v>49697.82103780847</v>
+        <v>34788.474726465916</v>
       </c>
       <c r="L21" s="42">
         <f t="shared" si="7"/>
-        <v>47398.780913627539</v>
+        <v>33179.146639539249</v>
       </c>
       <c r="M21" s="42">
         <f t="shared" si="7"/>
-        <v>46426.911907662521</v>
+        <v>32498.838335363798</v>
       </c>
       <c r="N21" s="42">
         <f t="shared" si="7"/>
-        <v>43836.507342461009</v>
+        <v>30685.555139722706</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -4978,51 +4978,51 @@
       </c>
       <c r="C22" s="40">
         <f t="shared" ref="C22:N22" si="8">C19-C21</f>
-        <v>60479.621153545188</v>
+        <v>42335.734807481684</v>
       </c>
       <c r="D22" s="40">
         <f t="shared" si="8"/>
-        <v>55282.646686166394</v>
+        <v>38697.852680316486</v>
       </c>
       <c r="E22" s="40">
         <f t="shared" si="8"/>
-        <v>53034.882340298122</v>
+        <v>37124.417638208753</v>
       </c>
       <c r="F22" s="40">
         <f t="shared" si="8"/>
-        <v>47701.714954536175</v>
+        <v>33391.200468175361</v>
       </c>
       <c r="G22" s="40">
         <f t="shared" si="8"/>
-        <v>45632.221664036762</v>
+        <v>31942.555164825731</v>
       </c>
       <c r="H22" s="40">
         <f t="shared" si="8"/>
-        <v>41042.192615860884</v>
+        <v>28729.534831102588</v>
       </c>
       <c r="I22" s="40">
         <f t="shared" si="8"/>
-        <v>159342.16231299206</v>
+        <v>111539.51361909442</v>
       </c>
       <c r="J22" s="40">
         <f t="shared" si="8"/>
-        <v>152432.61042556784</v>
+        <v>106702.8272978975</v>
       </c>
       <c r="K22" s="40">
         <f t="shared" si="8"/>
-        <v>149093.46311342542</v>
+        <v>104365.42417939776</v>
       </c>
       <c r="L22" s="40">
         <f t="shared" si="8"/>
-        <v>142196.34274088262</v>
+        <v>99537.439918617747</v>
       </c>
       <c r="M22" s="40">
         <f t="shared" si="8"/>
-        <v>139280.73572298756</v>
+        <v>97496.515006091387</v>
       </c>
       <c r="N22" s="40">
         <f t="shared" si="8"/>
-        <v>131509.52202738303</v>
+        <v>92056.665419168115</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -5138,51 +5138,51 @@
       </c>
       <c r="C30" s="4">
         <f t="shared" ref="C30:N30" si="9">C11/C27</f>
-        <v>2523.9434925663904</v>
+        <v>1766.7604447964734</v>
       </c>
       <c r="D30" s="4">
         <f t="shared" si="9"/>
-        <v>2483.618665662505</v>
+        <v>1738.5330659637534</v>
       </c>
       <c r="E30" s="4">
         <f t="shared" si="9"/>
-        <v>2480.141354970976</v>
+        <v>1736.098948479683</v>
       </c>
       <c r="F30" s="4">
         <f t="shared" si="9"/>
-        <v>2436.4274298177106</v>
+        <v>1705.4992008723973</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="9"/>
-        <v>2432.4333841959065</v>
+        <v>1702.7033689371344</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="9"/>
-        <v>2392.3737915416114</v>
+        <v>1674.6616540791279</v>
       </c>
       <c r="I30" s="4">
         <f t="shared" si="9"/>
-        <v>2854.9355130719173</v>
+        <v>1998.4548591503419</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="9"/>
-        <v>2808.4286480984611</v>
+        <v>1965.9000536689227</v>
       </c>
       <c r="K30" s="4">
         <f t="shared" si="9"/>
-        <v>2794.1176608699443</v>
+        <v>1955.8823626089609</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="9"/>
-        <v>2745.3921791995353</v>
+        <v>1921.7745254396741</v>
       </c>
       <c r="M30" s="4">
         <f t="shared" si="9"/>
-        <v>2738.9487160603421</v>
+        <v>1917.2641012422398</v>
       </c>
       <c r="N30" s="4">
         <f t="shared" si="9"/>
-        <v>2685.445447086629</v>
+        <v>1879.8118129606401</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -5191,51 +5191,51 @@
       </c>
       <c r="C31" s="4">
         <f t="shared" ref="C31:N31" si="10">C30*C28</f>
-        <v>630985.87314159761</v>
+        <v>441690.11119911837</v>
       </c>
       <c r="D31" s="4">
         <f t="shared" si="10"/>
-        <v>620904.6664156263</v>
+        <v>434633.26649093837</v>
       </c>
       <c r="E31" s="4">
         <f t="shared" si="10"/>
-        <v>620035.33874274394</v>
+        <v>434024.73711992078</v>
       </c>
       <c r="F31" s="4">
         <f t="shared" si="10"/>
-        <v>609106.85745442763</v>
+        <v>426374.80021809932</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="10"/>
-        <v>608108.34604897664</v>
+        <v>425675.84223428363</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" si="10"/>
-        <v>598093.44788540283</v>
+        <v>418665.41351978196</v>
       </c>
       <c r="I31" s="4">
         <f t="shared" si="10"/>
-        <v>799381.94366013689</v>
+        <v>559567.36056209577</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="10"/>
-        <v>786360.02146756905</v>
+        <v>550452.01502729836</v>
       </c>
       <c r="K31" s="4">
         <f t="shared" si="10"/>
-        <v>782352.94504358445</v>
+        <v>547647.06153050903</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="10"/>
-        <v>768709.81017586985</v>
+        <v>538096.86712310871</v>
       </c>
       <c r="M31" s="4">
         <f t="shared" si="10"/>
-        <v>766905.64049689576</v>
+        <v>536833.94834782719</v>
       </c>
       <c r="N31" s="4">
         <f t="shared" si="10"/>
-        <v>751924.72518425609</v>
+        <v>526347.30762897921</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -5290,51 +5290,51 @@
       </c>
       <c r="C35" s="4">
         <f t="shared" ref="C35:N35" si="11">C31*C34</f>
-        <v>126197.17462831952</v>
+        <v>88338.02223982368</v>
       </c>
       <c r="D35" s="4">
         <f t="shared" si="11"/>
-        <v>124180.93328312527</v>
+        <v>86926.653298187681</v>
       </c>
       <c r="E35" s="4">
         <f t="shared" si="11"/>
-        <v>124007.0677485488</v>
+        <v>86804.947423984166</v>
       </c>
       <c r="F35" s="4">
         <f t="shared" si="11"/>
-        <v>121821.37149088553</v>
+        <v>85274.960043619867</v>
       </c>
       <c r="G35" s="4">
         <f t="shared" si="11"/>
-        <v>121621.66920979533</v>
+        <v>85135.168446856725</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="11"/>
-        <v>119618.68957708057</v>
+        <v>83733.082703956403</v>
       </c>
       <c r="I35" s="4">
         <f t="shared" si="11"/>
-        <v>159876.38873202738</v>
+        <v>111913.47211241916</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="11"/>
-        <v>157272.00429351383</v>
+        <v>110090.40300545968</v>
       </c>
       <c r="K35" s="4">
         <f t="shared" si="11"/>
-        <v>156470.5890087169</v>
+        <v>109529.41230610182</v>
       </c>
       <c r="L35" s="4">
         <f t="shared" si="11"/>
-        <v>153741.96203517399</v>
+        <v>107619.37342462175</v>
       </c>
       <c r="M35" s="4">
         <f t="shared" si="11"/>
-        <v>153381.12809937916</v>
+        <v>107366.78966956545</v>
       </c>
       <c r="N35" s="4">
         <f t="shared" si="11"/>
-        <v>150384.94503685122</v>
+        <v>105269.46152579585</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -5387,51 +5387,51 @@
       </c>
       <c r="C38" s="4">
         <f t="shared" ref="C38:N38" si="12">C37*C35</f>
-        <v>3154.9293657079884</v>
+        <v>2208.4505559955919</v>
       </c>
       <c r="D38" s="4">
         <f t="shared" si="12"/>
-        <v>3104.5233320781317</v>
+        <v>2173.1663324546921</v>
       </c>
       <c r="E38" s="4">
         <f t="shared" si="12"/>
-        <v>3100.1766937137199</v>
+        <v>2170.1236855996044</v>
       </c>
       <c r="F38" s="4">
         <f t="shared" si="12"/>
-        <v>3045.5342872721385</v>
+        <v>2131.8740010904967</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="12"/>
-        <v>3040.5417302448836</v>
+        <v>2128.3792111714183</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="12"/>
-        <v>2990.4672394270146</v>
+        <v>2093.3270675989102</v>
       </c>
       <c r="I38" s="4">
         <f t="shared" si="12"/>
-        <v>3996.9097183006847</v>
+        <v>2797.8368028104792</v>
       </c>
       <c r="J38" s="4">
         <f t="shared" si="12"/>
-        <v>3931.8001073378459</v>
+        <v>2752.2600751364921</v>
       </c>
       <c r="K38" s="4">
         <f t="shared" si="12"/>
-        <v>3911.7647252179227</v>
+        <v>2738.2353076525455</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="12"/>
-        <v>3843.54905087935</v>
+        <v>2690.4843356155438</v>
       </c>
       <c r="M38" s="4">
         <f t="shared" si="12"/>
-        <v>3834.5282024844792</v>
+        <v>2684.1697417391365</v>
       </c>
       <c r="N38" s="4">
         <f t="shared" si="12"/>
-        <v>3759.6236259212806</v>
+        <v>2631.7365381448963</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
